--- a/16avos.xlsx
+++ b/16avos.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\esau_\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\esau_\Desktop\Jobs\Sites\Quiniela\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A10199DC-D373-4A0E-B0A7-08B3CE6BF7C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40B9F51C-4C15-48DB-94EF-425A03B7CB08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="24220" windowHeight="15500" xr2:uid="{4AA83B29-E214-4A04-86D4-91E6D9046809}"/>
+    <workbookView xWindow="28500" yWindow="1812" windowWidth="25284" windowHeight="12120" xr2:uid="{4AA83B29-E214-4A04-86D4-91E6D9046809}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="749" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="783" uniqueCount="57">
   <si>
     <t>Captura tus marcadores en las celdas azules, la primera posición corresponde al local y la segunda al visitante. ¡Asegúrate de llenar ambos campos!
 A partir de las fases de eliminación directa se toma como marcador válido para la quiniela, el marcador final al terminar el tiempo regular de juego, o en su caso, los tiempos extras.</t>
@@ -208,6 +208,9 @@
   </si>
   <si>
     <t xml:space="preserve">Jorge Alberto </t>
+  </si>
+  <si>
+    <t>Customer Service</t>
   </si>
 </sst>
 </file>
@@ -392,6 +395,15 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -403,15 +415,6 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -748,161 +751,167 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CCFACC23-6730-4775-B737-7B0E9594FFC7}">
-  <dimension ref="A1:DE21"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <dimension ref="A1:DK21"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="4" max="4" width="19.453125" customWidth="1"/>
+    <col min="4" max="4" width="19.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:109" ht="15" thickBot="1">
-      <c r="A1" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="13"/>
+    <row r="1" spans="1:115" ht="15" thickBot="1">
+      <c r="A1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="10"/>
     </row>
-    <row r="2" spans="1:109" ht="19" thickBot="1">
+    <row r="2" spans="1:115" ht="18.600000000000001" thickBot="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
     </row>
-    <row r="3" spans="1:109" ht="19" thickBot="1">
-      <c r="A3" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="9"/>
-      <c r="C3" s="9"/>
-      <c r="D3" s="10"/>
-      <c r="F3" s="8" t="s">
+    <row r="3" spans="1:115" ht="18.600000000000001" thickBot="1">
+      <c r="A3" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="12"/>
+      <c r="C3" s="12"/>
+      <c r="D3" s="13"/>
+      <c r="F3" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="G3" s="9"/>
-      <c r="H3" s="9"/>
-      <c r="I3" s="10"/>
-      <c r="K3" s="8" t="s">
+      <c r="G3" s="12"/>
+      <c r="H3" s="12"/>
+      <c r="I3" s="13"/>
+      <c r="K3" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="L3" s="9"/>
-      <c r="M3" s="9"/>
-      <c r="N3" s="10"/>
-      <c r="P3" s="8" t="s">
+      <c r="L3" s="12"/>
+      <c r="M3" s="12"/>
+      <c r="N3" s="13"/>
+      <c r="P3" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="Q3" s="9"/>
-      <c r="R3" s="9"/>
-      <c r="S3" s="10"/>
-      <c r="U3" s="8" t="s">
+      <c r="Q3" s="12"/>
+      <c r="R3" s="12"/>
+      <c r="S3" s="13"/>
+      <c r="U3" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="V3" s="9"/>
-      <c r="W3" s="9"/>
-      <c r="X3" s="10"/>
-      <c r="Z3" s="8" t="s">
+      <c r="V3" s="12"/>
+      <c r="W3" s="12"/>
+      <c r="X3" s="13"/>
+      <c r="Z3" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="AA3" s="9"/>
-      <c r="AB3" s="9"/>
-      <c r="AC3" s="10"/>
-      <c r="AE3" s="8" t="s">
+      <c r="AA3" s="12"/>
+      <c r="AB3" s="12"/>
+      <c r="AC3" s="13"/>
+      <c r="AE3" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="AF3" s="9"/>
-      <c r="AG3" s="9"/>
-      <c r="AH3" s="10"/>
-      <c r="AJ3" s="8" t="s">
+      <c r="AF3" s="12"/>
+      <c r="AG3" s="12"/>
+      <c r="AH3" s="13"/>
+      <c r="AJ3" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="AK3" s="9"/>
-      <c r="AL3" s="9"/>
-      <c r="AM3" s="10"/>
-      <c r="AO3" s="8" t="s">
+      <c r="AK3" s="12"/>
+      <c r="AL3" s="12"/>
+      <c r="AM3" s="13"/>
+      <c r="AO3" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="AP3" s="9"/>
-      <c r="AQ3" s="9"/>
-      <c r="AR3" s="10"/>
-      <c r="AT3" s="8" t="s">
+      <c r="AP3" s="12"/>
+      <c r="AQ3" s="12"/>
+      <c r="AR3" s="13"/>
+      <c r="AT3" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="AU3" s="9"/>
-      <c r="AV3" s="9"/>
-      <c r="AW3" s="10"/>
-      <c r="AY3" s="8" t="s">
+      <c r="AU3" s="12"/>
+      <c r="AV3" s="12"/>
+      <c r="AW3" s="13"/>
+      <c r="AY3" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="AZ3" s="9"/>
-      <c r="BA3" s="9"/>
-      <c r="BB3" s="10"/>
-      <c r="BD3" s="8" t="s">
+      <c r="AZ3" s="12"/>
+      <c r="BA3" s="12"/>
+      <c r="BB3" s="13"/>
+      <c r="BD3" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="BE3" s="9"/>
-      <c r="BF3" s="9"/>
-      <c r="BG3" s="10"/>
-      <c r="BI3" s="8" t="s">
+      <c r="BE3" s="12"/>
+      <c r="BF3" s="12"/>
+      <c r="BG3" s="13"/>
+      <c r="BI3" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="BJ3" s="9"/>
-      <c r="BK3" s="9"/>
-      <c r="BL3" s="10"/>
-      <c r="BN3" s="8" t="s">
+      <c r="BJ3" s="12"/>
+      <c r="BK3" s="12"/>
+      <c r="BL3" s="13"/>
+      <c r="BN3" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="BO3" s="9"/>
-      <c r="BP3" s="9"/>
-      <c r="BQ3" s="10"/>
-      <c r="BS3" s="8" t="s">
+      <c r="BO3" s="12"/>
+      <c r="BP3" s="12"/>
+      <c r="BQ3" s="13"/>
+      <c r="BS3" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="BT3" s="9"/>
-      <c r="BU3" s="9"/>
-      <c r="BV3" s="10"/>
-      <c r="BX3" s="8" t="s">
+      <c r="BT3" s="12"/>
+      <c r="BU3" s="12"/>
+      <c r="BV3" s="13"/>
+      <c r="BX3" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="BY3" s="9"/>
-      <c r="BZ3" s="9"/>
-      <c r="CA3" s="10"/>
-      <c r="CC3" s="8" t="s">
+      <c r="BY3" s="12"/>
+      <c r="BZ3" s="12"/>
+      <c r="CA3" s="13"/>
+      <c r="CC3" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="CD3" s="9"/>
-      <c r="CE3" s="9"/>
-      <c r="CF3" s="10"/>
-      <c r="CH3" s="8" t="s">
+      <c r="CD3" s="12"/>
+      <c r="CE3" s="12"/>
+      <c r="CF3" s="13"/>
+      <c r="CH3" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="CI3" s="9"/>
-      <c r="CJ3" s="9"/>
-      <c r="CK3" s="10"/>
-      <c r="CM3" s="8" t="s">
+      <c r="CI3" s="12"/>
+      <c r="CJ3" s="12"/>
+      <c r="CK3" s="13"/>
+      <c r="CM3" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="CN3" s="9"/>
-      <c r="CO3" s="9"/>
-      <c r="CP3" s="10"/>
-      <c r="CR3" s="8" t="s">
+      <c r="CN3" s="12"/>
+      <c r="CO3" s="12"/>
+      <c r="CP3" s="13"/>
+      <c r="CR3" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="CS3" s="9"/>
-      <c r="CT3" s="9"/>
-      <c r="CU3" s="10"/>
-      <c r="CW3" s="8" t="s">
+      <c r="CS3" s="12"/>
+      <c r="CT3" s="12"/>
+      <c r="CU3" s="13"/>
+      <c r="CW3" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="CX3" s="9"/>
-      <c r="CY3" s="9"/>
-      <c r="CZ3" s="10"/>
-      <c r="DB3" s="8" t="s">
+      <c r="CX3" s="12"/>
+      <c r="CY3" s="12"/>
+      <c r="CZ3" s="13"/>
+      <c r="DB3" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="DC3" s="9"/>
-      <c r="DD3" s="9"/>
-      <c r="DE3" s="10"/>
+      <c r="DC3" s="12"/>
+      <c r="DD3" s="12"/>
+      <c r="DE3" s="13"/>
+      <c r="DH3" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="DI3" s="12"/>
+      <c r="DJ3" s="12"/>
+      <c r="DK3" s="13"/>
     </row>
-    <row r="4" spans="1:109" ht="18.5">
+    <row r="4" spans="1:115" ht="18">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -991,8 +1000,12 @@
       <c r="DC4" s="1"/>
       <c r="DD4" s="1"/>
       <c r="DE4" s="1"/>
+      <c r="DH4" s="1"/>
+      <c r="DI4" s="1"/>
+      <c r="DJ4" s="1"/>
+      <c r="DK4" s="1"/>
     </row>
-    <row r="5" spans="1:109" ht="18.5">
+    <row r="5" spans="1:115" ht="18">
       <c r="A5" s="2" t="s">
         <v>2</v>
       </c>
@@ -1126,8 +1139,14 @@
       <c r="DC5" s="3"/>
       <c r="DD5" s="2"/>
       <c r="DE5" s="3"/>
+      <c r="DH5" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="DI5" s="3"/>
+      <c r="DJ5" s="2"/>
+      <c r="DK5" s="3"/>
     </row>
-    <row r="6" spans="1:109">
+    <row r="6" spans="1:115">
       <c r="A6" s="4" t="s">
         <v>3</v>
       </c>
@@ -1393,8 +1412,20 @@
       <c r="DE6" s="5">
         <v>0</v>
       </c>
+      <c r="DH6" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="DI6" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="DJ6" s="5">
+        <v>4</v>
+      </c>
+      <c r="DK6" s="5">
+        <v>1</v>
+      </c>
     </row>
-    <row r="7" spans="1:109">
+    <row r="7" spans="1:115">
       <c r="A7" s="4" t="s">
         <v>5</v>
       </c>
@@ -1660,8 +1691,20 @@
       <c r="DE7" s="5">
         <v>1</v>
       </c>
+      <c r="DH7" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="DI7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="DJ7" s="5">
+        <v>3</v>
+      </c>
+      <c r="DK7" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="8" spans="1:109">
+    <row r="8" spans="1:115">
       <c r="A8" s="4" t="s">
         <v>7</v>
       </c>
@@ -1927,8 +1970,16 @@
       <c r="DE8" s="5">
         <v>1</v>
       </c>
+      <c r="DH8" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="DI8" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="DJ8" s="5"/>
+      <c r="DK8" s="5"/>
     </row>
-    <row r="9" spans="1:109">
+    <row r="9" spans="1:115">
       <c r="A9" s="4" t="s">
         <v>9</v>
       </c>
@@ -2194,8 +2245,20 @@
       <c r="DE9" s="5">
         <v>0</v>
       </c>
+      <c r="DH9" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="DI9" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="DJ9" s="5">
+        <v>1</v>
+      </c>
+      <c r="DK9" s="5">
+        <v>1</v>
+      </c>
     </row>
-    <row r="10" spans="1:109">
+    <row r="10" spans="1:115">
       <c r="A10" s="4" t="s">
         <v>11</v>
       </c>
@@ -2461,8 +2524,20 @@
       <c r="DE10" s="5">
         <v>0</v>
       </c>
+      <c r="DH10" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="DI10" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="DJ10" s="5">
+        <v>2</v>
+      </c>
+      <c r="DK10" s="5">
+        <v>2</v>
+      </c>
     </row>
-    <row r="11" spans="1:109">
+    <row r="11" spans="1:115">
       <c r="A11" s="4" t="s">
         <v>13</v>
       </c>
@@ -2728,8 +2803,20 @@
       <c r="DE11" s="5">
         <v>0</v>
       </c>
+      <c r="DH11" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="DI11" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="DJ11" s="5">
+        <v>2</v>
+      </c>
+      <c r="DK11" s="5">
+        <v>1</v>
+      </c>
     </row>
-    <row r="12" spans="1:109">
+    <row r="12" spans="1:115">
       <c r="A12" s="4" t="s">
         <v>15</v>
       </c>
@@ -2995,8 +3082,20 @@
       <c r="DE12" s="5">
         <v>0</v>
       </c>
+      <c r="DH12" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="DI12" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="DJ12" s="5">
+        <v>1</v>
+      </c>
+      <c r="DK12" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="13" spans="1:109">
+    <row r="13" spans="1:115">
       <c r="A13" s="4" t="s">
         <v>17</v>
       </c>
@@ -3262,8 +3361,20 @@
       <c r="DE13" s="5">
         <v>1</v>
       </c>
+      <c r="DH13" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="DI13" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="DJ13" s="5">
+        <v>1</v>
+      </c>
+      <c r="DK13" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:109">
+    <row r="14" spans="1:115">
       <c r="A14" s="4" t="s">
         <v>19</v>
       </c>
@@ -3529,8 +3640,20 @@
       <c r="DE14" s="5">
         <v>2</v>
       </c>
+      <c r="DH14" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="DI14" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="DJ14" s="5">
+        <v>2</v>
+      </c>
+      <c r="DK14" s="5">
+        <v>2</v>
+      </c>
     </row>
-    <row r="15" spans="1:109">
+    <row r="15" spans="1:115">
       <c r="A15" s="4" t="s">
         <v>21</v>
       </c>
@@ -3796,8 +3919,20 @@
       <c r="DE15" s="5">
         <v>2</v>
       </c>
+      <c r="DH15" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="DI15" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="DJ15" s="5">
+        <v>2</v>
+      </c>
+      <c r="DK15" s="5">
+        <v>1</v>
+      </c>
     </row>
-    <row r="16" spans="1:109">
+    <row r="16" spans="1:115">
       <c r="A16" s="4" t="s">
         <v>23</v>
       </c>
@@ -4063,8 +4198,20 @@
       <c r="DE16" s="5">
         <v>1</v>
       </c>
+      <c r="DH16" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="DI16" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="DJ16" s="5">
+        <v>2</v>
+      </c>
+      <c r="DK16" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="17" spans="1:109">
+    <row r="17" spans="1:115">
       <c r="A17" s="4" t="s">
         <v>25</v>
       </c>
@@ -4330,8 +4477,20 @@
       <c r="DE17" s="5">
         <v>1</v>
       </c>
+      <c r="DH17" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="DI17" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="DJ17" s="5">
+        <v>2</v>
+      </c>
+      <c r="DK17" s="5">
+        <v>1</v>
+      </c>
     </row>
-    <row r="18" spans="1:109">
+    <row r="18" spans="1:115">
       <c r="A18" s="4" t="s">
         <v>27</v>
       </c>
@@ -4597,8 +4756,20 @@
       <c r="DE18" s="5">
         <v>0</v>
       </c>
+      <c r="DH18" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="DI18" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="DJ18" s="5">
+        <v>4</v>
+      </c>
+      <c r="DK18" s="5">
+        <v>1</v>
+      </c>
     </row>
-    <row r="19" spans="1:109">
+    <row r="19" spans="1:115">
       <c r="A19" s="4" t="s">
         <v>29</v>
       </c>
@@ -4864,8 +5035,20 @@
       <c r="DE19" s="5">
         <v>2</v>
       </c>
+      <c r="DH19" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="DI19" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="DJ19" s="5">
+        <v>0</v>
+      </c>
+      <c r="DK19" s="5">
+        <v>2</v>
+      </c>
     </row>
-    <row r="20" spans="1:109">
+    <row r="20" spans="1:115">
       <c r="A20" s="4" t="s">
         <v>31</v>
       </c>
@@ -5131,8 +5314,20 @@
       <c r="DE20" s="5">
         <v>0</v>
       </c>
+      <c r="DH20" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="DI20" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="DJ20" s="5">
+        <v>1</v>
+      </c>
+      <c r="DK20" s="5">
+        <v>1</v>
+      </c>
     </row>
-    <row r="21" spans="1:109">
+    <row r="21" spans="1:115">
       <c r="A21" s="4" t="s">
         <v>33</v>
       </c>
@@ -5398,16 +5593,22 @@
       <c r="DE21" s="5">
         <v>1</v>
       </c>
+      <c r="DH21" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="DI21" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="DJ21" s="5">
+        <v>2</v>
+      </c>
+      <c r="DK21" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="23">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="P3:S3"/>
-    <mergeCell ref="Z3:AC3"/>
-    <mergeCell ref="F3:I3"/>
-    <mergeCell ref="K3:N3"/>
-    <mergeCell ref="U3:X3"/>
+  <mergeCells count="24">
+    <mergeCell ref="DH3:DK3"/>
     <mergeCell ref="AE3:AH3"/>
     <mergeCell ref="AY3:BB3"/>
     <mergeCell ref="BN3:BQ3"/>
@@ -5424,6 +5625,13 @@
     <mergeCell ref="BX3:CA3"/>
     <mergeCell ref="CC3:CF3"/>
     <mergeCell ref="CH3:CK3"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="P3:S3"/>
+    <mergeCell ref="Z3:AC3"/>
+    <mergeCell ref="F3:I3"/>
+    <mergeCell ref="K3:N3"/>
+    <mergeCell ref="U3:X3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId1"/>
